--- a/MSME/Test upload format/MSME_Continuity - 2.xlsx
+++ b/MSME/Test upload format/MSME_Continuity - 2.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet 1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$1:$H$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet 1'!$A$1:$H$25</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +56,7 @@
     <t>NPAInterestAmount</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357192</t>
+    <t>CGMSMGEN2210202600357238</t>
   </si>
   <si>
     <t>Aloan01</t>
@@ -68,19 +68,19 @@
     <t>31-01-2028</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357193</t>
+    <t>CGMSMGEN2210202600357239</t>
   </si>
   <si>
     <t>Aloan02</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357194</t>
+    <t>CGMSMGEN2210202600357240</t>
   </si>
   <si>
     <t>Aloan03</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357195</t>
+    <t>CGMSMGEN2210202600357241</t>
   </si>
   <si>
     <t>Aloan04</t>
@@ -89,121 +89,121 @@
     <t>Standard</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357196</t>
+    <t>CGMSMGEN2210202600357242</t>
   </si>
   <si>
     <t>Aloan05</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357197</t>
+    <t>CGMSMGEN2210202600357243</t>
   </si>
   <si>
     <t>Aloan06</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357198</t>
+    <t>CGMSMGEN2210202600357244</t>
   </si>
   <si>
     <t>Aloan07</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357199</t>
+    <t>CGMSMGEN2210202600357245</t>
   </si>
   <si>
     <t>Aloan08</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357200</t>
+    <t>CGMSMGEN2210202600357246</t>
   </si>
   <si>
     <t>Aloan09</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357201</t>
+    <t>CGMSMGEN2210202600357247</t>
   </si>
   <si>
     <t>Aloan10</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357202</t>
+    <t>CGMSMGEN2210202600357248</t>
   </si>
   <si>
     <t>Aloan11</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357203</t>
+    <t>CGMSMGEN2210202600357249</t>
   </si>
   <si>
     <t>Aloan12</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357204</t>
+    <t>CGMSMGEN2210202600357250</t>
   </si>
   <si>
     <t>Aloan13</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357205</t>
+    <t>CGMSMGEN2210202600357251</t>
   </si>
   <si>
     <t>Aloan14</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357206</t>
+    <t>CGMSMGEN2210202600357252</t>
   </si>
   <si>
     <t>Aloan15</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357207</t>
+    <t>CGMSMGEN2210202600357253</t>
   </si>
   <si>
     <t>Aloan16</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357208</t>
+    <t>CGMSMGEN2210202600357254</t>
   </si>
   <si>
     <t>Aloan17</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357209</t>
+    <t>CGMSMGEN2210202600357255</t>
   </si>
   <si>
     <t>Aloan18</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357210</t>
+    <t>CGMSMGEN2210202600357256</t>
   </si>
   <si>
     <t>Aloan19</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357211</t>
+    <t>CGMSMGEN2210202600357257</t>
   </si>
   <si>
     <t>Aloan20</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357212</t>
+    <t>CGMSMGEN2210202600357258</t>
   </si>
   <si>
     <t>Aloan21</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357213</t>
+    <t>CGMSMGEN2210202600357259</t>
   </si>
   <si>
     <t>Aloan22</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357214</t>
+    <t>CGMSMGEN2210202600357260</t>
   </si>
   <si>
     <t>Aloan23</t>
   </si>
   <si>
-    <t>CGMSMGEN2209202600357215</t>
+    <t>CGMSMGEN2210202600357261</t>
   </si>
   <si>
     <t>Aloan24</t>
@@ -871,7 +871,7 @@
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -879,6 +879,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -888,9 +891,10 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1156,15 +1160,15 @@
   <dimension ref="A1:H25"/>
   <sheetFormatPr defaultColWidth="12.6666666666667" defaultRowHeight="12.75" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="33.4285714285714" style="3" customWidth="1"/>
-    <col min="2" max="2" width="22.7809523809524" style="3" customWidth="1"/>
-    <col min="3" max="3" width="34.2857142857143" style="3" customWidth="1"/>
-    <col min="4" max="4" width="21.2857142857143" style="4" customWidth="1"/>
-    <col min="5" max="5" width="25.7142857142857" style="3" customWidth="1"/>
-    <col min="6" max="6" width="30.2857142857143" style="4" customWidth="1"/>
-    <col min="7" max="7" width="38" style="3" customWidth="1"/>
-    <col min="8" max="8" width="28.1428571428571" style="3" customWidth="1"/>
-    <col min="9" max="16384" width="12.6666666666667" style="3"/>
+    <col min="1" max="1" width="33.4285714285714" style="4" customWidth="1"/>
+    <col min="2" max="2" width="22.7809523809524" style="4" customWidth="1"/>
+    <col min="3" max="3" width="34.2857142857143" style="4" customWidth="1"/>
+    <col min="4" max="4" width="21.2857142857143" style="5" customWidth="1"/>
+    <col min="5" max="5" width="25.7142857142857" style="4" customWidth="1"/>
+    <col min="6" max="6" width="30.2857142857143" style="5" customWidth="1"/>
+    <col min="7" max="7" width="38" style="4" customWidth="1"/>
+    <col min="8" max="8" width="28.1428571428571" style="4" customWidth="1"/>
+    <col min="9" max="16384" width="12.6666666666667" style="4"/>
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:8">
@@ -1183,7 +1187,7 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
@@ -1194,10 +1198,10 @@
       </c>
     </row>
     <row r="2" s="2" customFormat="1" ht="15" spans="1:8">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C2" s="8">
@@ -1220,10 +1224,10 @@
       </c>
     </row>
     <row r="3" s="2" customFormat="1" ht="15" spans="1:8">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="8" t="s">
         <v>13</v>
       </c>
       <c r="C3" s="8">
@@ -1246,10 +1250,10 @@
       </c>
     </row>
     <row r="4" s="2" customFormat="1" ht="15" spans="1:8">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="8" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="8">
@@ -1275,7 +1279,7 @@
       <c r="A5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="8" t="s">
         <v>17</v>
       </c>
       <c r="C5" s="8">
@@ -1295,7 +1299,7 @@
       <c r="A6" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="8" t="s">
         <v>20</v>
       </c>
       <c r="C6" s="8">
@@ -1315,7 +1319,7 @@
       <c r="A7" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>22</v>
       </c>
       <c r="C7" s="8">
@@ -1332,10 +1336,10 @@
       <c r="H7" s="8"/>
     </row>
     <row r="8" ht="15" spans="1:8">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>24</v>
       </c>
       <c r="C8" s="8">
@@ -1352,10 +1356,10 @@
       <c r="H8" s="8"/>
     </row>
     <row r="9" ht="15" spans="1:8">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C9" s="8">
@@ -1378,10 +1382,10 @@
       </c>
     </row>
     <row r="10" ht="15" spans="1:8">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>28</v>
       </c>
       <c r="C10" s="8">
@@ -1407,7 +1411,7 @@
       <c r="A11" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>30</v>
       </c>
       <c r="C11" s="8">
@@ -1433,7 +1437,7 @@
       <c r="A12" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>32</v>
       </c>
       <c r="C12" s="8">
@@ -1453,7 +1457,7 @@
       <c r="A13" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>34</v>
       </c>
       <c r="C13" s="8">
@@ -1473,7 +1477,7 @@
       <c r="A14" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C14" s="8">
@@ -1499,7 +1503,7 @@
       <c r="A15" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="8" t="s">
         <v>38</v>
       </c>
       <c r="C15" s="8">
@@ -1525,7 +1529,7 @@
       <c r="A16" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="8" t="s">
         <v>40</v>
       </c>
       <c r="C16" s="8">
@@ -1551,7 +1555,7 @@
       <c r="A17" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="8" t="s">
         <v>42</v>
       </c>
       <c r="C17" s="8">
@@ -1571,7 +1575,7 @@
       <c r="A18" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="8" t="s">
         <v>44</v>
       </c>
       <c r="C18" s="8">
@@ -1591,7 +1595,7 @@
       <c r="A19" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="8" t="s">
         <v>46</v>
       </c>
       <c r="C19" s="8">
@@ -1611,7 +1615,7 @@
       <c r="A20" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="8" t="s">
         <v>48</v>
       </c>
       <c r="C20" s="8">
@@ -1627,81 +1631,81 @@
       <c r="G20" s="8"/>
       <c r="H20" s="8"/>
     </row>
-    <row r="21" ht="15" spans="1:8">
-      <c r="A21" s="7" t="s">
+    <row r="21" s="3" customFormat="1" ht="15" spans="1:8">
+      <c r="A21" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="8">
+      <c r="C21" s="10">
         <v>100000000</v>
       </c>
-      <c r="D21" s="8">
-        <v>0</v>
-      </c>
-      <c r="E21" s="8" t="s">
+      <c r="D21" s="10">
+        <v>0</v>
+      </c>
+      <c r="E21" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G21" s="8">
+      <c r="G21" s="10">
         <v>10000000</v>
       </c>
-      <c r="H21" s="8">
+      <c r="H21" s="10">
         <v>100</v>
       </c>
     </row>
-    <row r="22" ht="15" spans="1:8">
-      <c r="A22" s="7" t="s">
+    <row r="22" s="3" customFormat="1" ht="15" spans="1:8">
+      <c r="A22" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="B22" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="8">
+      <c r="C22" s="10">
         <v>150000000</v>
       </c>
-      <c r="D22" s="8">
-        <v>0</v>
-      </c>
-      <c r="E22" s="8" t="s">
+      <c r="D22" s="10">
+        <v>0</v>
+      </c>
+      <c r="E22" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F22" s="8" t="s">
+      <c r="F22" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G22" s="8">
+      <c r="G22" s="10">
         <v>50000000</v>
       </c>
-      <c r="H22" s="8">
+      <c r="H22" s="10">
         <v>100</v>
       </c>
     </row>
-    <row r="23" ht="15" spans="1:8">
-      <c r="A23" s="7" t="s">
+    <row r="23" s="3" customFormat="1" ht="15" spans="1:8">
+      <c r="A23" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="B23" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="8">
+      <c r="C23" s="10">
         <v>100000000</v>
       </c>
-      <c r="D23" s="8">
-        <v>0</v>
-      </c>
-      <c r="E23" s="8" t="s">
+      <c r="D23" s="10">
+        <v>0</v>
+      </c>
+      <c r="E23" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="F23" s="8" t="s">
+      <c r="F23" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="G23" s="8">
+      <c r="G23" s="10">
         <v>10000000</v>
       </c>
-      <c r="H23" s="8">
+      <c r="H23" s="10">
         <v>0</v>
       </c>
     </row>
@@ -1709,7 +1713,7 @@
       <c r="A24" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="7" t="s">
+      <c r="B24" s="8" t="s">
         <v>56</v>
       </c>
       <c r="C24" s="8">
@@ -1729,7 +1733,7 @@
       <c r="A25" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="8" t="s">
         <v>58</v>
       </c>
       <c r="C25" s="8">
@@ -1746,7 +1750,7 @@
       <c r="H25" s="8"/>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H21" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H25" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
